--- a/Introudction in Pyhton EXCEL/12605178.xlsx
+++ b/Introudction in Pyhton EXCEL/12605178.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -255,6 +255,15 @@
   </si>
   <si>
     <t xml:space="preserve">Revising C++ and Database </t>
+  </si>
+  <si>
+    <t>Not doing anything just cleaning my bedsheet, some clothes and revising they things which taught by our database mam and networking sir.</t>
+  </si>
+  <si>
+    <t>Doing some C++ questions to build logic</t>
+  </si>
+  <si>
+    <t>Saturday (Holiday)</t>
   </si>
 </sst>
 </file>
@@ -1494,49 +1503,97 @@
         <v>72</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+    <row r="16" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="13">
+        <v>46224</v>
+      </c>
+      <c r="B16" s="14">
+        <v>450</v>
+      </c>
+      <c r="C16" s="14">
+        <v>30</v>
+      </c>
+      <c r="D16" s="14">
+        <v>180</v>
+      </c>
+      <c r="E16" s="14">
+        <v>0</v>
+      </c>
+      <c r="F16" s="14">
+        <v>300</v>
+      </c>
+      <c r="G16" s="14">
+        <v>6</v>
+      </c>
+      <c r="H16" s="14">
+        <v>0</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+        <v>480</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="90" x14ac:dyDescent="0.25">
+      <c r="A17" s="13">
+        <v>46225</v>
+      </c>
+      <c r="B17" s="14">
+        <v>450</v>
+      </c>
+      <c r="C17" s="14">
+        <v>30</v>
+      </c>
+      <c r="D17" s="14">
+        <v>180</v>
+      </c>
+      <c r="E17" s="14">
+        <v>0</v>
+      </c>
+      <c r="F17" s="14">
+        <v>0</v>
+      </c>
+      <c r="G17" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="H17" s="14">
+        <v>0</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>660</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>780</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="13"/>
@@ -1547,14 +1604,8 @@
       <c r="F18" s="14"/>
       <c r="G18" s="14"/>
       <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
       <c r="K18" s="16"/>
       <c r="L18" s="16"/>
       <c r="M18" s="16"/>

--- a/Introudction in Pyhton EXCEL/12605178.xlsx
+++ b/Introudction in Pyhton EXCEL/12605178.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -264,6 +264,12 @@
   </si>
   <si>
     <t>Saturday (Holiday)</t>
+  </si>
+  <si>
+    <t>Sunday</t>
+  </si>
+  <si>
+    <t>Notes making and some personal work also.And pratice to build topology also using CISCO packet tracer</t>
   </si>
 </sst>
 </file>
@@ -1595,21 +1601,51 @@
         <v>73</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15"/>
-      <c r="J18" s="15"/>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+    <row r="18" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+      <c r="A18" s="13">
+        <v>46226</v>
+      </c>
+      <c r="B18" s="14">
+        <v>360</v>
+      </c>
+      <c r="C18" s="14">
+        <v>30</v>
+      </c>
+      <c r="D18" s="14">
+        <v>180</v>
+      </c>
+      <c r="E18" s="14">
+        <v>120</v>
+      </c>
+      <c r="F18" s="14">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="H18" s="14">
+        <v>70</v>
+      </c>
+      <c r="I18" s="15">
+        <f t="shared" si="0"/>
+        <v>760</v>
+      </c>
+      <c r="J18" s="15">
+        <f t="shared" si="1"/>
+        <v>680</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="13"/>

--- a/Introudction in Pyhton EXCEL/12605178.xlsx
+++ b/Introudction in Pyhton EXCEL/12605178.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -270,6 +270,9 @@
   </si>
   <si>
     <t>Notes making and some personal work also.And pratice to build topology also using CISCO packet tracer</t>
+  </si>
+  <si>
+    <t>Stressed, and very different feeling coming out means very low.</t>
   </si>
 </sst>
 </file>
@@ -1647,27 +1650,51 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+    <row r="19" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+      <c r="A19" s="13">
+        <v>46227</v>
+      </c>
+      <c r="B19" s="14">
+        <v>450</v>
+      </c>
+      <c r="C19" s="14">
+        <v>30</v>
+      </c>
+      <c r="D19" s="14">
+        <v>0</v>
+      </c>
+      <c r="E19" s="14">
+        <v>0</v>
+      </c>
+      <c r="F19" s="14">
+        <v>300</v>
+      </c>
+      <c r="G19" s="14">
+        <v>6</v>
+      </c>
+      <c r="H19" s="14">
+        <v>0</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>780</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>660</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="13"/>

--- a/Introudction in Pyhton EXCEL/12605178.xlsx
+++ b/Introudction in Pyhton EXCEL/12605178.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -273,6 +273,15 @@
   </si>
   <si>
     <t>Stressed, and very different feeling coming out means very low.</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>Pratice some topology like Point-to-Point, Bus, Mesh, Star, daisy, etc.</t>
   </si>
 </sst>
 </file>
@@ -1696,27 +1705,49 @@
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
+    <row r="20" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+      <c r="A20" s="13">
+        <v>46228</v>
+      </c>
+      <c r="B20" s="14">
+        <v>450</v>
+      </c>
+      <c r="C20" s="14">
+        <v>60</v>
+      </c>
+      <c r="D20" s="14">
+        <v>300</v>
+      </c>
+      <c r="E20" s="14">
+        <v>0</v>
+      </c>
+      <c r="F20" s="14">
+        <v>250</v>
+      </c>
+      <c r="G20" s="14">
+        <v>5</v>
+      </c>
       <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>380</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="13"/>

--- a/Introudction in Pyhton EXCEL/12605178.xlsx
+++ b/Introudction in Pyhton EXCEL/12605178.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -282,6 +282,9 @@
   </si>
   <si>
     <t>Pratice some topology like Point-to-Point, Bus, Mesh, Star, daisy, etc.</t>
+  </si>
+  <si>
+    <t>Making Notes ADVANCED DATABASE TECHNIQUES</t>
   </si>
 </sst>
 </file>
@@ -1749,27 +1752,51 @@
         <v>81</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+    <row r="21" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="13">
+        <v>46229</v>
+      </c>
+      <c r="B21" s="14">
+        <v>450</v>
+      </c>
+      <c r="C21" s="14">
+        <v>30</v>
+      </c>
+      <c r="D21" s="14">
+        <v>180</v>
+      </c>
+      <c r="E21" s="14">
+        <v>0</v>
+      </c>
+      <c r="F21" s="14">
+        <v>250</v>
+      </c>
+      <c r="G21" s="14">
+        <v>5</v>
+      </c>
+      <c r="H21" s="14">
+        <v>0</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>530</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="13"/>

--- a/Introudction in Pyhton EXCEL/12605178.xlsx
+++ b/Introudction in Pyhton EXCEL/12605178.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -285,6 +285,9 @@
   </si>
   <si>
     <t>Making Notes ADVANCED DATABASE TECHNIQUES</t>
+  </si>
+  <si>
+    <t>Learning Python basics via practicing challenges, problems and understanding the concepts also in VS code</t>
   </si>
 </sst>
 </file>
@@ -1798,27 +1801,51 @@
         <v>82</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+    <row r="22" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+      <c r="A22" s="13">
+        <v>46230</v>
+      </c>
+      <c r="B22" s="14">
+        <v>450</v>
+      </c>
+      <c r="C22" s="14">
+        <v>30</v>
+      </c>
+      <c r="D22" s="14">
+        <v>0</v>
+      </c>
+      <c r="E22" s="14">
+        <v>180</v>
+      </c>
+      <c r="F22" s="14">
+        <v>300</v>
+      </c>
+      <c r="G22" s="14">
+        <v>6</v>
+      </c>
+      <c r="H22" s="14">
+        <v>0</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>480</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="13"/>

--- a/Introudction in Pyhton EXCEL/12605178.xlsx
+++ b/Introudction in Pyhton EXCEL/12605178.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -288,6 +288,9 @@
   </si>
   <si>
     <t>Learning Python basics via practicing challenges, problems and understanding the concepts also in VS code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nothing Just chilling with some friends </t>
   </si>
 </sst>
 </file>
@@ -1847,27 +1850,51 @@
         <v>83</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+    <row r="23" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="13">
+        <v>46231</v>
+      </c>
+      <c r="B23" s="14">
+        <v>450</v>
+      </c>
+      <c r="C23" s="14">
+        <v>0</v>
+      </c>
+      <c r="D23" s="14">
+        <v>0</v>
+      </c>
+      <c r="E23" s="14">
+        <v>0</v>
+      </c>
+      <c r="F23" s="14">
+        <v>350</v>
+      </c>
+      <c r="G23" s="14">
+        <v>7</v>
+      </c>
+      <c r="H23" s="14">
+        <v>0</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>800</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+        <v>640</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="13"/>

--- a/Introudction in Pyhton EXCEL/12605178.xlsx
+++ b/Introudction in Pyhton EXCEL/12605178.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="87">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -291,6 +291,12 @@
   </si>
   <si>
     <t xml:space="preserve">Nothing Just chilling with some friends </t>
+  </si>
+  <si>
+    <t>Makeup class their But Cancelled</t>
+  </si>
+  <si>
+    <t>One day's ended I figured out that I have not done one single productive work which makes my day's feeling at end low and unsatisified</t>
   </si>
 </sst>
 </file>
@@ -1896,27 +1902,51 @@
         <v>84</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+    <row r="24" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+      <c r="A24" s="13">
+        <v>46232</v>
+      </c>
+      <c r="B24" s="14">
+        <v>450</v>
+      </c>
+      <c r="C24" s="14">
+        <v>30</v>
+      </c>
+      <c r="D24" s="14">
+        <v>0</v>
+      </c>
+      <c r="E24" s="14">
+        <v>0</v>
+      </c>
+      <c r="F24" s="14">
+        <v>0</v>
+      </c>
+      <c r="G24" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="H24" s="14">
+        <v>0</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>480</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>960</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="13"/>

--- a/Introudction in Pyhton EXCEL/12605178.xlsx
+++ b/Introudction in Pyhton EXCEL/12605178.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="88">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -297,6 +297,10 @@
   </si>
   <si>
     <t>One day's ended I figured out that I have not done one single productive work which makes my day's feeling at end low and unsatisified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Today, I filed an RMS complaint for my lost laptop charger, learned Python basics with ChatGPT for my Minor and Major Projects, revised C++, planned to revise Java, took care of my grooming, washed some clothes, and ended the day with my last game.
+</t>
   </si>
 </sst>
 </file>
@@ -1948,27 +1952,51 @@
         <v>86</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+    <row r="25" spans="1:14" ht="165" x14ac:dyDescent="0.25">
+      <c r="A25" s="13">
+        <v>46233</v>
+      </c>
+      <c r="B25" s="14">
+        <v>480</v>
+      </c>
+      <c r="C25" s="14">
+        <v>30</v>
+      </c>
+      <c r="D25" s="14">
+        <v>0</v>
+      </c>
+      <c r="E25" s="14">
+        <v>120</v>
+      </c>
+      <c r="F25" s="14">
+        <v>0</v>
+      </c>
+      <c r="G25" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="H25" s="14">
+        <v>60</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>690</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+        <v>750</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="13"/>

--- a/Introudction in Pyhton EXCEL/12605178.xlsx
+++ b/Introudction in Pyhton EXCEL/12605178.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -301,6 +301,9 @@
   <si>
     <t xml:space="preserve">Today, I filed an RMS complaint for my lost laptop charger, learned Python basics with ChatGPT for my Minor and Major Projects, revised C++, planned to revise Java, took care of my grooming, washed some clothes, and ended the day with my last game.
 </t>
+  </si>
+  <si>
+    <t>Today I run so fast in track, and after coming back I have done some logic building questions to code more better and revise today's topic of Database and Communication</t>
   </si>
 </sst>
 </file>
@@ -1998,27 +2001,51 @@
         <v>87</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+    <row r="26" spans="1:14" ht="105" x14ac:dyDescent="0.25">
+      <c r="A26" s="13">
+        <v>46234</v>
+      </c>
+      <c r="B26" s="14">
+        <v>450</v>
+      </c>
+      <c r="C26" s="14">
+        <v>45</v>
+      </c>
+      <c r="D26" s="14">
+        <v>30</v>
+      </c>
+      <c r="E26" s="14">
+        <v>60</v>
+      </c>
+      <c r="F26" s="14">
+        <v>100</v>
+      </c>
+      <c r="G26" s="14">
+        <v>2</v>
+      </c>
+      <c r="H26" s="14">
+        <v>30</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>715</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>725</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13"/>

--- a/Introudction in Pyhton EXCEL/12605178.xlsx
+++ b/Introudction in Pyhton EXCEL/12605178.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -206,9 +206,6 @@
     <t>MCA - D2635</t>
   </si>
   <si>
-    <t>August</t>
-  </si>
-  <si>
     <t>Stressed</t>
   </si>
   <si>
@@ -304,6 +301,12 @@
   </si>
   <si>
     <t>Today I run so fast in track, and after coming back I have done some logic building questions to code more better and revise today's topic of Database and Communication</t>
+  </si>
+  <si>
+    <t>September</t>
+  </si>
+  <si>
+    <t>Preparing for Data Networking and Communicationn CA exam, and other personal works also</t>
   </si>
 </sst>
 </file>
@@ -1017,7 +1020,7 @@
         <v>33</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="G3" s="20"/>
     </row>
@@ -1163,16 +1166,16 @@
         <v>520</v>
       </c>
       <c r="K7" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L7" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="L7" s="16" t="s">
+      <c r="M7" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M7" s="16" t="s">
+      <c r="N7" s="17" t="s">
         <v>59</v>
-      </c>
-      <c r="N7" s="17" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="75" x14ac:dyDescent="0.25">
@@ -1218,7 +1221,7 @@
         <v>51</v>
       </c>
       <c r="N8" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="75" x14ac:dyDescent="0.25">
@@ -1264,7 +1267,7 @@
         <v>51</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="60" x14ac:dyDescent="0.25">
@@ -1287,7 +1290,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H10" s="14">
         <v>0</v>
@@ -1304,13 +1307,13 @@
         <v>49</v>
       </c>
       <c r="L10" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M10" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="150" x14ac:dyDescent="0.25">
@@ -1333,7 +1336,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H11" s="14">
         <v>255</v>
@@ -1353,10 +1356,10 @@
         <v>50</v>
       </c>
       <c r="M11" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="75" x14ac:dyDescent="0.25">
@@ -1379,7 +1382,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H12" s="14">
         <v>0</v>
@@ -1396,13 +1399,13 @@
         <v>49</v>
       </c>
       <c r="L12" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M12" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="105" x14ac:dyDescent="0.25">
@@ -1445,10 +1448,10 @@
         <v>50</v>
       </c>
       <c r="M13" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="60" x14ac:dyDescent="0.25">
@@ -1491,10 +1494,10 @@
         <v>50</v>
       </c>
       <c r="M14" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="N14" s="17" t="s">
         <v>70</v>
-      </c>
-      <c r="N14" s="17" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
@@ -1540,7 +1543,7 @@
         <v>51</v>
       </c>
       <c r="N15" s="17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="30" x14ac:dyDescent="0.25">
@@ -1577,16 +1580,16 @@
         <v>480</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M16" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="90" x14ac:dyDescent="0.25">
@@ -1609,7 +1612,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H17" s="14">
         <v>0</v>
@@ -1623,16 +1626,16 @@
         <v>780</v>
       </c>
       <c r="K17" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L17" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M17" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M17" s="16" t="s">
-        <v>59</v>
-      </c>
       <c r="N17" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="60" x14ac:dyDescent="0.25">
@@ -1655,7 +1658,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H18" s="14">
         <v>70</v>
@@ -1669,16 +1672,16 @@
         <v>680</v>
       </c>
       <c r="K18" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L18" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M18" s="16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="45" x14ac:dyDescent="0.25">
@@ -1715,16 +1718,16 @@
         <v>660</v>
       </c>
       <c r="K19" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L19" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M19" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="45" x14ac:dyDescent="0.25">
@@ -1759,16 +1762,16 @@
         <v>380</v>
       </c>
       <c r="K20" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="L20" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="L20" s="16" t="s">
+      <c r="M20" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="N20" s="17" t="s">
         <v>80</v>
-      </c>
-      <c r="M20" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="N20" s="17" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="30" x14ac:dyDescent="0.25">
@@ -1805,16 +1808,16 @@
         <v>530</v>
       </c>
       <c r="K21" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L21" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M21" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N21" s="17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="60" x14ac:dyDescent="0.25">
@@ -1860,7 +1863,7 @@
         <v>51</v>
       </c>
       <c r="N22" s="17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="30" x14ac:dyDescent="0.25">
@@ -1897,16 +1900,16 @@
         <v>640</v>
       </c>
       <c r="K23" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L23" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M23" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N23" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="75" x14ac:dyDescent="0.25">
@@ -1929,7 +1932,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H24" s="14">
         <v>0</v>
@@ -1943,16 +1946,16 @@
         <v>960</v>
       </c>
       <c r="K24" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L24" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M24" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N24" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="165" x14ac:dyDescent="0.25">
@@ -1975,7 +1978,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H25" s="14">
         <v>60</v>
@@ -1989,16 +1992,16 @@
         <v>750</v>
       </c>
       <c r="K25" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L25" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M25" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N25" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="105" x14ac:dyDescent="0.25">
@@ -2041,33 +2044,57 @@
         <v>50</v>
       </c>
       <c r="M26" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N26" s="17" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+      <c r="A27" s="13">
+        <v>46235</v>
+      </c>
+      <c r="B27" s="14">
+        <v>450</v>
+      </c>
+      <c r="C27" s="14">
+        <v>60</v>
+      </c>
+      <c r="D27" s="14">
+        <v>120</v>
+      </c>
+      <c r="E27" s="14">
+        <v>0</v>
+      </c>
+      <c r="F27" s="14">
+        <v>250</v>
+      </c>
+      <c r="G27" s="14">
+        <v>5</v>
+      </c>
+      <c r="H27" s="14">
+        <v>30</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>530</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13"/>

--- a/Introudction in Pyhton EXCEL/12605178.xlsx
+++ b/Introudction in Pyhton EXCEL/12605178.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="91">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -307,6 +307,10 @@
   </si>
   <si>
     <t>Preparing for Data Networking and Communicationn CA exam, and other personal works also</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Today, I attended Python, C++, Database, and Networking practicals. I learned Python Lists, C++ recursion, database keys and DML commands. I also understood the OSI Model and practiced router connections in Cisco Packet Tracer. Additionally, I revised C++ Unit 1 and 2 concepts through coding.
+</t>
   </si>
 </sst>
 </file>
@@ -1134,7 +1138,7 @@
     </row>
     <row r="7" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="13">
-        <v>46215</v>
+        <v>46246</v>
       </c>
       <c r="B7" s="14">
         <v>330</v>
@@ -1180,7 +1184,7 @@
     </row>
     <row r="8" spans="1:14" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" s="13">
-        <v>46216</v>
+        <v>46247</v>
       </c>
       <c r="B8" s="14">
         <v>240</v>
@@ -1226,7 +1230,7 @@
     </row>
     <row r="9" spans="1:14" ht="75" x14ac:dyDescent="0.25">
       <c r="A9" s="13">
-        <v>46217</v>
+        <v>46248</v>
       </c>
       <c r="B9" s="14">
         <v>240</v>
@@ -1272,7 +1276,7 @@
     </row>
     <row r="10" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="13">
-        <v>46218</v>
+        <v>46249</v>
       </c>
       <c r="B10" s="14">
         <v>360</v>
@@ -1318,7 +1322,7 @@
     </row>
     <row r="11" spans="1:14" ht="150" x14ac:dyDescent="0.25">
       <c r="A11" s="13">
-        <v>46219</v>
+        <v>46250</v>
       </c>
       <c r="B11" s="14">
         <v>360</v>
@@ -1364,7 +1368,7 @@
     </row>
     <row r="12" spans="1:14" ht="75" x14ac:dyDescent="0.25">
       <c r="A12" s="13">
-        <v>46220</v>
+        <v>46251</v>
       </c>
       <c r="B12" s="14">
         <v>450</v>
@@ -1410,7 +1414,7 @@
     </row>
     <row r="13" spans="1:14" ht="105" x14ac:dyDescent="0.25">
       <c r="A13" s="13">
-        <v>46221</v>
+        <v>46252</v>
       </c>
       <c r="B13" s="14">
         <v>360</v>
@@ -1456,7 +1460,7 @@
     </row>
     <row r="14" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="13">
-        <v>46222</v>
+        <v>46253</v>
       </c>
       <c r="B14" s="14">
         <v>420</v>
@@ -1502,7 +1506,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13">
-        <v>46223</v>
+        <v>46254</v>
       </c>
       <c r="B15" s="14">
         <v>450</v>
@@ -1548,7 +1552,7 @@
     </row>
     <row r="16" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="13">
-        <v>46224</v>
+        <v>46255</v>
       </c>
       <c r="B16" s="14">
         <v>450</v>
@@ -1594,7 +1598,7 @@
     </row>
     <row r="17" spans="1:14" ht="90" x14ac:dyDescent="0.25">
       <c r="A17" s="13">
-        <v>46225</v>
+        <v>46256</v>
       </c>
       <c r="B17" s="14">
         <v>450</v>
@@ -1640,7 +1644,7 @@
     </row>
     <row r="18" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="13">
-        <v>46226</v>
+        <v>46257</v>
       </c>
       <c r="B18" s="14">
         <v>360</v>
@@ -1686,7 +1690,7 @@
     </row>
     <row r="19" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="13">
-        <v>46227</v>
+        <v>46258</v>
       </c>
       <c r="B19" s="14">
         <v>450</v>
@@ -1732,7 +1736,7 @@
     </row>
     <row r="20" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="13">
-        <v>46228</v>
+        <v>46259</v>
       </c>
       <c r="B20" s="14">
         <v>450</v>
@@ -1776,7 +1780,7 @@
     </row>
     <row r="21" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="13">
-        <v>46229</v>
+        <v>46260</v>
       </c>
       <c r="B21" s="14">
         <v>450</v>
@@ -1822,7 +1826,7 @@
     </row>
     <row r="22" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="13">
-        <v>46230</v>
+        <v>46261</v>
       </c>
       <c r="B22" s="14">
         <v>450</v>
@@ -1868,7 +1872,7 @@
     </row>
     <row r="23" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="13">
-        <v>46231</v>
+        <v>46262</v>
       </c>
       <c r="B23" s="14">
         <v>450</v>
@@ -1914,7 +1918,7 @@
     </row>
     <row r="24" spans="1:14" ht="75" x14ac:dyDescent="0.25">
       <c r="A24" s="13">
-        <v>46232</v>
+        <v>46263</v>
       </c>
       <c r="B24" s="14">
         <v>450</v>
@@ -1960,7 +1964,7 @@
     </row>
     <row r="25" spans="1:14" ht="165" x14ac:dyDescent="0.25">
       <c r="A25" s="13">
-        <v>46233</v>
+        <v>46264</v>
       </c>
       <c r="B25" s="14">
         <v>480</v>
@@ -2006,7 +2010,7 @@
     </row>
     <row r="26" spans="1:14" ht="105" x14ac:dyDescent="0.25">
       <c r="A26" s="13">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="B26" s="14">
         <v>450</v>
@@ -2052,7 +2056,7 @@
     </row>
     <row r="27" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A27" s="13">
-        <v>46235</v>
+        <v>46266</v>
       </c>
       <c r="B27" s="14">
         <v>450</v>
@@ -2096,27 +2100,51 @@
         <v>89</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+    <row r="28" spans="1:14" ht="195" x14ac:dyDescent="0.25">
+      <c r="A28" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B28" s="14">
+        <v>450</v>
+      </c>
+      <c r="C28" s="14">
+        <v>30</v>
+      </c>
+      <c r="D28" s="14">
+        <v>150</v>
+      </c>
+      <c r="E28" s="14">
+        <v>60</v>
+      </c>
+      <c r="F28" s="14">
+        <v>250</v>
+      </c>
+      <c r="G28" s="14">
+        <v>5</v>
+      </c>
+      <c r="H28" s="14">
+        <v>30</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>970</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>470</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="13"/>

--- a/Introudction in Pyhton EXCEL/12605178.xlsx
+++ b/Introudction in Pyhton EXCEL/12605178.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="92">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -311,6 +311,9 @@
   <si>
     <t xml:space="preserve">Today, I attended Python, C++, Database, and Networking practicals. I learned Python Lists, C++ recursion, database keys and DML commands. I also understood the OSI Model and practiced router connections in Cisco Packet Tracer. Additionally, I revised C++ Unit 1 and 2 concepts through coding.
 </t>
+  </si>
+  <si>
+    <t>Learning Basics of Python, and preparing for Database and Networking</t>
   </si>
 </sst>
 </file>
@@ -2146,27 +2149,51 @@
         <v>90</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+    <row r="29" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+      <c r="A29" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B29" s="14">
+        <v>450</v>
+      </c>
+      <c r="C29" s="14">
+        <v>30</v>
+      </c>
+      <c r="D29" s="14">
+        <v>150</v>
+      </c>
+      <c r="E29" s="14">
+        <v>30</v>
+      </c>
+      <c r="F29" s="14">
+        <v>300</v>
+      </c>
+      <c r="G29" s="14">
+        <v>6</v>
+      </c>
+      <c r="H29" s="14">
+        <v>30</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>450</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="13"/>

--- a/Introudction in Pyhton EXCEL/12605178.xlsx
+++ b/Introudction in Pyhton EXCEL/12605178.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="93">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -314,6 +314,9 @@
   </si>
   <si>
     <t>Learning Basics of Python, and preparing for Database and Networking</t>
+  </si>
+  <si>
+    <t>Learning OSI model and doing practice set of C++ which teaches by our professor</t>
   </si>
 </sst>
 </file>
@@ -2195,27 +2198,51 @@
         <v>91</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+    <row r="30" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+      <c r="A30" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B30" s="14">
+        <v>450</v>
+      </c>
+      <c r="C30" s="14">
+        <v>30</v>
+      </c>
+      <c r="D30" s="14">
+        <v>150</v>
+      </c>
+      <c r="E30" s="14">
+        <v>30</v>
+      </c>
+      <c r="F30" s="14">
+        <v>350</v>
+      </c>
+      <c r="G30" s="14">
+        <v>7</v>
+      </c>
+      <c r="H30" s="14">
+        <v>30</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>400</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="13"/>
